--- a/docs/samples/review_list.xlsx
+++ b/docs/samples/review_list.xlsx
@@ -12,8 +12,8 @@
     <sheet name="填写说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'疑似重复'!$A$1:$R$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'异常清单'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'疑似重复'!$A$1:$S$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'异常清单'!$A$1:$K$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,27 +437,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="39" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="70" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="39" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="70" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,85 +469,90 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>疑似组</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>触发原因</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>置信度</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>A 编号</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>A 名称</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>A 产品</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>A 来源</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>B 编号</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>B 名称</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>B 产品</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>B 来源</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>冲突字段</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>缺失信息</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>建议动作</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>当前状态</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>decision</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -559,1071 +565,1108 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>共用 OE 且类别/车型/尺寸/位置全部一致；合并会使同一产品内出现冲突</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>B:B05X</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Fan Shroud</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>P-000005</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>A:A-42-00</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Fan Shroud</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>P-000054</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>供应商A报价表_v2.xlsx!报价明细!R28</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>合并后 A:A-05-00 与 A:A-42-00 会进入同一产品（同一供应商的两个编号），规则不做这种传递合并，请人工确认。 规则已自动归一；如判断有误，可在产品页拆分。</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>共用 OE 但关键属性冲突</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>A:A-06-00</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-31-L</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>P-000006</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R7</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B:B06X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B32R</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>P-000057</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>尺寸: 151x91x20 vs 151x91x14</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>位置: left vs right</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>OE-FRC-2001 同时出现在 A:A-06-00（Front Grille）与 B:B06X（Front Grille），冲突：尺寸：A:A-06-00=151x91x20 vs B:B06X=151x91x14。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>OE-SHARED-03 同时出现在 A:A-31-L（Side Grille）与 B:B32R（Side Grille），冲突：位置：A:A-31-L=left vs B:B32R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>共用 OE 但关键属性冲突；缺少关键信息</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>共用 OE 但关键属性冲突</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>A:A-12-L</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>A:A-40-L</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Side Grille, Left side</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>P-000012</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>B:B13R</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>B:B41R</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>位置: left vs right</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>尺寸、车型年份</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>OE-VN-1010 同时出现在 A:A-12-L（Side Grille）与 B:B13R（Side Grille），冲突：位置：A:A-12-L=left vs B:B13R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 缺少尺寸、车型年份，判断依据不足。</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>OE-CONFLICT-02 同时出现在 A:A-40-L（Side Grille）与 B:B41R（Side Grille），冲突：位置：A:A-40-L=left vs B:B41R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>共用 OE 但关键属性冲突</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>A:A-27-00</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-03-L</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>P-000021</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+          <t>P-000003</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>B:B28X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P-000046</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+          <t>P-000059</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>类别: Front Grille vs Bug Screen；尺寸: 122x75x7 vs 120x75x8</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>位置: left vs right</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>OE-SHARED-01 同时出现在 A:A-27-00（Front Grille）与 B:B28X（Bug Screen），冲突：类别：A:A-27-00=Front Grille vs B:B28X=Bug Screen；尺寸：A:A-27-00=122x75x7 vs B:B28X=120x75x8。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>OE-VNL-1003 同时出现在 A:A-03-L（Side Grille）与 C:C-1003-R（Side Grille），冲突：位置：A:A-03-L=left vs C:C-1003-R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>共用 OE 但关键属性冲突</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>A:A-29-00</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.619</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>A:A-03-L</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>P-000022</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
+          <t>P-000003</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>B:B30X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>A:A-31-L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>类别: Air Filter Housing vs Air Filter Housing Cap；尺寸: 121x22x92 vs 32x32x8</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1003 vs OE-SHARED-03（软）</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>OE-SHARED-02 同时出现在 A:A-29-00（Air Filter Housing）与 B:B30X（Air Filter Housing Cap），冲突：类别：A:A-29-00=Air Filter Housing vs B:B30X=Air Filter Housing Cap；尺寸：A:A-29-00=121x22x92 vs B:B30X=32x32x8。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-VNL-1003 vs OE-SHARED-03），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>共用 OE 但关键属性冲突</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>A:A-31-L</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.619</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>A:A-03-L</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Side Grille, Left side</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>P-000023</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
+          <t>P-000003</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>B:B32R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-40-L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>位置: left vs right</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1003 vs OE-CONFLICT-02（软）</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>OE-SHARED-03 同时出现在 A:A-31-L（Side Grille）与 B:B32R（Side Grille），冲突：位置：A:A-31-L=left vs B:B32R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-VNL-1003 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>共用 OE 但关键属性冲突</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>A:A-38-00</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.619</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-31-L</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>P-000026</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>B:B39X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>A:A-40-L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>P-000052</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>类别: Front Grille vs Bug Screen</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>OE 号: OE-SHARED-03 vs OE-CONFLICT-02（软）</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>OE-CONFLICT-01 同时出现在 A:A-38-00（Front Grille）与 B:B39X（Bug Screen），冲突：类别：A:A-38-00=Front Grille vs B:B39X=Bug Screen。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>共用 OE 但关键属性冲突</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>A:A-40-L</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.619</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>A:A-04-R</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>Side Grille, Right side</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>P-000004</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>B:B41R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>B:B32R</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>位置: left vs right</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1004 vs OE-SHARED-03（软）</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>OE-CONFLICT-02 同时出现在 A:A-40-L（Side Grille）与 B:B41R（Side Grille），冲突：位置：A:A-40-L=left vs B:B41R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-SHARED-03），可能是不同代次或替代件，请核对。</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>共用 OE 但关键属性冲突</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>A:A-03-L</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.619</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B04R</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>P-000003</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
+          <t>P-000004</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C:C-1003-R</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>B:B41R</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>Side Grille</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>P-000060</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>位置: left vs right</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1004 vs OE-CONFLICT-02（软）</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>OE-VNL-1003 同时出现在 A:A-03-L（Side Grille）与 C:C-1003-R（Side Grille），冲突：位置：A:A-03-L=left vs C:C-1003-R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>共用 OE 但关键信息缺失；缺少关键信息</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>A:A-10-00</t>
-        </is>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.619</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>B:B32R</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>P-000010</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R11</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C:C-2005</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Radiator Fan Shroud</t>
+          <t>B:B41R</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P-000062</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r6</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OE 号: OE-SHARED-03 vs OE-CONFLICT-02（软）</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>尺寸</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>共用 OE-FRC-2005，但缺少尺寸。请补充资料后重新导入，或在核实后确认合并。</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>166</v>
       </c>
       <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>0.619</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>A:A-03-L</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B04R</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>P-000003</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
+          <t>P-000004</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>A:A-31-L</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
+          <t>P-000059</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1003 vs OE-SHARED-03（软）</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1004 vs OE-VNL-1003（软）</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1003 vs OE-SHARED-03），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>0.619</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>A:A-03-L</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B32R</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>P-000003</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>A:A-40-L</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>P-000059</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1003 vs OE-CONFLICT-02（软）</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>OE 号: OE-SHARED-03 vs OE-VNL-1003（软）</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1003 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>0.619</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>A:A-31-L</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B41R</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>A:A-40-L</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>P-000059</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>OE 号: OE-SHARED-03 vs OE-CONFLICT-02（软）</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>OE 号: OE-CONFLICT-02 vs OE-VNL-1003（软）</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-CONFLICT-02 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>0.619</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>A:A-04-R</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Side Grille, Right side</t>
+          <t>A:A-03-L</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>P-000004</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
+          <t>P-000003</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>B:B32R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-17-L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1004 vs OE-SHARED-03（软）</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1633,75 +1676,78 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-SHARED-03），可能是不同代次或替代件，请核对。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>0.619</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>B:B04R</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-17-L</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>P-000004</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>B:B41R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>A:A-31-L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1004 vs OE-CONFLICT-02（软）</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1711,75 +1757,78 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>0.619</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>B:B32R</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-17-L</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>B:B41R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>A:A-40-L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>OE 号: OE-SHARED-03 vs OE-CONFLICT-02（软）</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1789,75 +1838,78 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>166</v>
+        <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>0.619</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>B:B04R</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>A:A-04-R</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Side Grille, Right side</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>P-000004</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>B:B18R</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>Right Side Grille</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>P-000004</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>C:C-1003-R</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Side Grille</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>P-000060</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1004 vs OE-VNL-1003（软）</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1867,77 +1919,80 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>0.619</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>B:B18R</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Right Side Grille</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>P-000042</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>B:B32R</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Right Side Grille</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>P-000048</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>C:C-1003-R</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Side Grille</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>P-000060</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>OE 号: OE-SHARED-03 vs OE-VNL-1003（软）</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>—</t>
@@ -1945,77 +2000,80 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>0.619</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>B:B18R</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Right Side Grille</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>P-000042</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>B:B41R</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Side Grille</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>P-000053</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>C:C-1003-R</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Side Grille</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>P-000060</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>OE 号: OE-CONFLICT-02 vs OE-VNL-1003（软）</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>—</t>
@@ -2023,75 +2081,78 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-CONFLICT-02 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>173</v>
+      </c>
+      <c r="B21" t="n">
         <v>2</v>
       </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>A:A-01-00</t>
-        </is>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.619</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B18R</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>P-000001</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>A:A-27-00</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>P-000021</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+          <t>P-000059</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1001 vs OE-SHARED-01（软）</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2101,153 +2162,159 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1001 vs OE-SHARED-01），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>A:A-08-00</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>共用 OE 但关键属性冲突；缺少关键信息</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>A:A-12-L</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>P-000008</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>A:A-29-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>B:B13R</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>P-000022</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>OE 号: OE-FRC-2003 vs OE-SHARED-02（软）</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>位置: left vs right</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-FRC-2003 vs OE-SHARED-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>尺寸、车型年份</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
+          <t>OE-VN-1010 同时出现在 A:A-12-L（Side Grille）与 B:B13R（Side Grille），冲突：位置：A:A-12-L=left vs B:B13R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 缺少尺寸、车型年份，判断依据不足。</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>A:A-02-00</t>
-        </is>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.619</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>A:A-12-L</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>P-000002</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>B:B28X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>A:A-25-L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>P-000046</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+          <t>P-000020</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1002 vs OE-SHARED-01（软）</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2257,75 +2324,78 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1002 vs OE-SHARED-01），可能是不同代次或替代件，请核对。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>A:A-09-00</t>
-        </is>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.619</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>B:B26R</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>P-000009</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
+          <t>P-000045</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>B:B30X</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>A:A-43-R</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>Side Grille, Right side</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>P-000055</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>OE 号: OE-FRC-2004 vs OE-SHARED-02（软）</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2335,75 +2405,78 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-FRC-2004 vs OE-SHARED-02），可能是不同代次或替代件，请核对。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>属性一致但 OE 号不同</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>A:A-38-00</t>
-        </is>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；缺少关键信息</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.476</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-12-L</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>P-000026</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>B:B06X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B36L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P-000057</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>OE 号: OE-CONFLICT-01 vs OE-FRC-2001（软）</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2413,2749 +2486,2778 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-CONFLICT-01 vs OE-FRC-2001），可能是不同代次或替代件，请核对。</t>
+          <t>OE 号、适配车型</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少适配车型，判断依据不足。</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
         <v>4</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>A:A-03-L</t>
-        </is>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；缺少关键信息</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.476</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>A:A-25-L</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>Side Grille, Left side</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>P-000003</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
+          <t>P-000020</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>A:A-17-L</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B36L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE 号、适配车型</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少适配车型，判断依据不足。</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
         <v>4</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>A:A-12-L</t>
-        </is>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号；缺少关键信息</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.476</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B13R</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>P-000012</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>A:A-25-L</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B26R</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>P-000020</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
+          <t>P-000045</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE 号、尺寸、车型年份</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 缺少尺寸、车型年份，判断依据不足。</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>A:A-17-L</t>
-        </is>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；缺少关键信息</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.476</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B13R</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>A:A-31-L</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>A:A-43-R</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>Side Grille, Right side</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
+          <t>P-000055</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE 号、尺寸、车型年份</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少尺寸、车型年份，判断依据不足。</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>A:A-17-L</t>
-        </is>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>共用 OE 但关键属性冲突；包装尺寸不同（仅提示）</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>A:A-27-00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
+          <t>P-000021</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>A:A-40-L</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>B:B28X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>P-000046</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>类别: Front Grille vs Bug Screen；尺寸: 122x75x7 vs 120x75x8（软）</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
+          <t>OE-SHARED-01 同时出现在 A:A-27-00（Front Grille）与 B:B28X（Bug Screen），冲突：类别：A:A-27-00=Front Grille vs B:B28X=Bug Screen。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 包装尺寸不同（122x75x7 vs 120x75x8），可能是换了包装，也可能是录入错误，仅作提示。</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>A:A-04-R</t>
-        </is>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Side Grille, Right side</t>
+          <t>A:A-01-00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>P-000004</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
+          <t>P-000001</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>B:B18R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-27-00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>P-000021</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>OE 号: OE-VNL-1001 vs OE-SHARED-01（软）</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-VNL-1001 vs OE-SHARED-01），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>B:B18R</t>
-        </is>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-02-00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>P-000002</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>B:B32R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>B:B28X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>P-000046</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>OE 号: OE-VNL-1002 vs OE-SHARED-01（软）</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-VNL-1002 vs OE-SHARED-01），可能是不同代次或替代件，请核对。</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>B:B18R</t>
-        </is>
+      <c r="E32" t="n">
+        <v>0.579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-01-00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>P-000001</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>B:B41R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>A:A-14-00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>P-000013</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>B:B26R</t>
-        </is>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-02-00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>P-000045</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
+          <t>P-000002</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A:A-43-R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Side Grille, Right side</t>
+          <t>A:A-16-00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>P-000055</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
+          <t>P-000014</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R15</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>B:B18R</t>
-        </is>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-14-00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>P-000013</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C:C-1003-R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>A:A-27-00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>P-000060</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>P-000021</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
         <v>0.579</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>A:A-01-00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Front Grille</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>P-000001</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>A:A-14-00</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>B:B15X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>Front Grille</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>P-000013</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="B36" t="n">
         <v>4</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
         <v>0.579</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>A:A-02-00</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>A:A-14-00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>P-000002</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
+          <t>P-000013</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A:A-16-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>B:B15X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>P-000014</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R15</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>0.579</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>A:A-08-00</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>A:A-16-00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>P-000008</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
+          <t>P-000014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>A:A-19-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>B:B28X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>P-000016</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R17</t>
+          <t>P-000046</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>0.579</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>A:A-10-00</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>A:A-27-00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>P-000010</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R11</t>
+          <t>P-000021</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>A:A-21-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>B:B15X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>P-000017</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R18</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>A:A-11-00</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>共用 OE 但关键属性冲突；包装尺寸不同（仅提示）</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-29-00</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>P-000011</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
+          <t>P-000022</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>A:A-24-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B30X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>P-000019</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>类别: Air Filter Housing vs Air Filter Housing Cap；尺寸: 121x22x92 vs 32x32x8（软）</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
+          <t>OE-SHARED-02 同时出现在 A:A-29-00（Air Filter Housing）与 B:B30X（Air Filter Housing Cap），冲突：类别：A:A-29-00=Air Filter Housing vs B:B30X=Air Filter Housing Cap。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 包装尺寸不同（121x22x92 vs 32x32x8），可能是换了包装，也可能是录入错误，仅作提示。</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
         <v>0.579</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>A:A-11-00</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-08-00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>P-000011</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
+          <t>P-000008</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>A:A-33-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-29-00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
+          <t>P-000022</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>OE 号: OE-FRC-2003 vs OE-SHARED-02（软）</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-FRC-2003 vs OE-SHARED-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
         <v>0.579</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>A:A-14-00</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-09-00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>P-000013</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
+          <t>P-000009</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>A:A-27-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B30X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>P-000021</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>OE 号: OE-FRC-2004 vs OE-SHARED-02（软）</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-FRC-2004 vs OE-SHARED-02），可能是不同代次或替代件，请核对。</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>0.579</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>A:A-08-00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Air Filter Housing</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>P-000008</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>A:A-19-00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Air Filter Housing</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>P-000016</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>供应商A报价表_v2.xlsx!报价明细!R17</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>A:A-29-00</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Air Filter Housing</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>P-000022</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="n">
         <v>4</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>0.579</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>A:A-22-00</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-19-00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>P-000018</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
+          <t>P-000016</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>A:A-38-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R17</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-29-00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>P-000026</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
+          <t>P-000022</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="n">
         <v>4</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
         <v>0.579</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>A:A-24-00</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-09-00</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>P-000019</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
+          <t>P-000009</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>A:A-33-00</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B20X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>0.579</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>A:A-01-00</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-09-00</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>P-000001</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
+          <t>P-000009</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>B:B15X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B37X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>P-000041</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="n">
         <v>4</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
         <v>0.579</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>A:A-07-00</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>B:B20X</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>P-000007</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R8</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>B:B23X</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>B:B30X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>P-000044</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="n">
         <v>4</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
         <v>0.579</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>A:A-09-00</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>B:B20X</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>Air Filter Housing Cap</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>P-000009</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>B:B20X</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>B:B37X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>Air Filter Housing Cap</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>P-000043</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="n">
         <v>4</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
         <v>0.579</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>A:A-09-00</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>B:B30X</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>Air Filter Housing Cap</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>P-000009</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>B:B37X</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Air Filter Housing Cap</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>P-000051</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>A:A-14-00</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>共用 OE 但关键属性冲突</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>A:A-38-00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>Front Grille</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>P-000013</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
+          <t>P-000026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>B:B15X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B39X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>P-000041</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+          <t>P-000052</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>类别: Front Grille vs Bug Screen</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
+          <t>OE-CONFLICT-01 同时出现在 A:A-38-00（Front Grille）与 B:B39X（Bug Screen），冲突：类别：A:A-38-00=Front Grille vs B:B39X=Bug Screen。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
+        <v>6</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
         <v>0.579</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>A:A-16-00</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>A:A-38-00</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>P-000014</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R15</t>
+          <t>P-000026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>B:B28X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>B:B06X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>P-000046</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+          <t>P-000006</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>OE 号: OE-CONFLICT-01 vs OE-FRC-2001（软）</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-CONFLICT-01 vs OE-FRC-2001），可能是不同代次或替代件，请核对。</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>A:A-22-00</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>属性一致但 OE 号不同；包装尺寸不同（仅提示）</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.421</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>A:A-07-00</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>P-000018</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
+          <t>P-000007</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>B:B06X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R8</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>B:B39X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>P-000057</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
+          <t>P-000052</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>OE 号: OE-FRC-2002 vs OE-CONFLICT-01（软）；尺寸: 147x11x90 vs 151x91x14（软）</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
+          <t>属性一致但 OE 号不同（OE-FRC-2002 vs OE-CONFLICT-01），可能是不同代次或替代件，请核对。 包装尺寸不同（147x11x90 vs 151x91x14），可能是换了包装，也可能是录入错误，仅作提示。</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="B52" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" t="n">
         <v>4</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
         <v>0.579</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>A:A-27-00</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>A:A-22-00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>Front Grille</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>P-000021</t>
-        </is>
-      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+          <t>P-000018</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>B:B15X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>A:A-38-00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>Front Grille</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>P-000041</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+          <t>P-000026</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="B53" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
         <v>0.579</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>B:B20X</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>A:A-07-00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>P-000043</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>P-000007</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>B:B30X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>B:B23X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>P-000044</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="B54" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" t="n">
         <v>4</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
         <v>0.579</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>B:B20X</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>A:A-22-00</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>P-000043</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>P-000018</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>B:B37X</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>B:B06X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>P-000006</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B55" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" t="n">
         <v>4</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>B:B30X</t>
-        </is>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号；包装尺寸不同（仅提示）</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.421</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>B:B23X</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>P-000044</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>B:B37X</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>B:B39X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>P-000052</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
+          <t>尺寸: 147x11x90 vs 151x91x14（软）</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
           <t>OE 号</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 包装尺寸不同（147x11x90 vs 151x91x14），可能是换了包装，也可能是录入错误，仅作提示。</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="n">
         <v>4</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；缺少关键信息</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>A:A-12-L</t>
-        </is>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.579</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>A:A-10-00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>P-000012</t>
+          <t>Fan Shroud</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
+          <t>P-000010</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>B:B36L</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R11</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Left Side Grille</t>
+          <t>A:A-21-00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>P-000050</t>
+          <t>Fan Shroud</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+          <t>P-000017</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R18</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>OE 号、适配车型</t>
-        </is>
-      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 缺少适配车型，判断依据不足。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="B57" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" t="n">
         <v>4</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；缺少关键信息</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>A:A-25-L</t>
-        </is>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.579</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>A:A-11-00</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>P-000020</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
+          <t>P-000011</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>B:B36L</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Left Side Grille</t>
+          <t>A:A-24-00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>P-000050</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+          <t>P-000019</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>OE 号、适配车型</t>
-        </is>
-      </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 缺少适配车型，判断依据不足。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="B58" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" t="n">
         <v>4</v>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号；缺少关键信息</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>B:B13R</t>
-        </is>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-11-00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>P-000011</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>B:B26R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-33-00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>P-000045</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
+          <t>P-000024</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>OE 号、尺寸、车型年份</t>
-        </is>
-      </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 缺少尺寸、车型年份，判断依据不足。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="B59" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" t="n">
         <v>4</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；缺少关键信息</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>B:B13R</t>
-        </is>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>A:A-24-00</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>P-000019</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>A:A-43-R</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Side Grille, Right side</t>
+          <t>A:A-33-00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>P-000055</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
+          <t>P-000024</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>OE 号、尺寸、车型年份</t>
-        </is>
-      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 缺少尺寸、车型年份，判断依据不足。</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>156</v>
-      </c>
-      <c r="B60" t="n">
-        <v>4</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>无共同 OE，仅属性一致；缺少关键信息</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>A:A-21-00</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Fan Shroud</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>P-000017</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R18</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>C:C-2005</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Radiator Fan Shroud</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>P-000062</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>供应商C目录.pdf!p1!t1!r6</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>OE 号、尺寸</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸一致；请查看图片或向供应商索要 OE 号后确认。 缺少尺寸，判断依据不足。</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R60"/>
+  <autoFilter ref="A1:S59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5166,7 +5268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5241,7 +5343,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -5288,7 +5390,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5331,7 +5433,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -5366,7 +5468,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -5374,7 +5476,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -5388,28 +5490,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>缺少OE 号、车型、尺寸，无法与其他记录比对，归入待补充</t>
+          <t>缺少OE 号、类别，无法与其他记录比对，归入待补充</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A-35-00</t>
+          <t>C-9001</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>P-000025</t>
+          <t>P-000064</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R26</t>
+          <t>供应商C目录.pdf!p2!t1!r2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -5417,7 +5519,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -5426,33 +5528,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_FOR_MATCHING</t>
+          <t>KEY_ATTR_CHANGED</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>缺少OE 号、类别，无法与其他记录比对，归入待补充</t>
+          <t>关键属性变化：dims: [151.0, 91.0, 14.0] → [151.0, 91.0, 20.0]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C-9001</t>
+          <t>A-06-00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>P-000065</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>P-000006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>key_attrs</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p2!t1!r2</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -5460,7 +5566,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -5469,12 +5575,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KEY_ATTR_CHANGED</t>
+          <t>MISSING_CURRENCY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>关键属性变化：dims: [151.0, 91.0, 14.0] → [151.0, 91.0, 20.0]</t>
+          <t>缺少币种</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5484,22 +5590,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A-06-00</t>
+          <t>A-33-00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>P-000006</t>
+          <t>P-000024</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>key_attrs</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R7</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -5507,7 +5613,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -5526,17 +5632,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A-33-00</t>
+          <t>B34X</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>P-000049</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5546,7 +5652,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -5554,7 +5660,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -5563,37 +5669,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MISSING_CURRENCY</t>
+          <t>MISSING_DIMS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>缺少币种</t>
+          <t>缺少尺寸</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B34X</t>
+          <t>A-35-00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>P-000049</t>
+          <t>P-000025</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>package_dims</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -5601,7 +5707,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -5620,17 +5726,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>A-35-00</t>
+          <t>B13R</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>P-000025</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5640,7 +5746,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -5648,7 +5754,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -5667,17 +5773,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>B13R</t>
+          <t>C-2005</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>P-000010</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5687,7 +5793,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>供应商C目录.pdf!p1!t1!r6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -5695,7 +5801,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -5704,37 +5810,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MISSING_DIMS</t>
+          <t>MISSING_FITMENT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>缺少尺寸</t>
+          <t>缺少适配车型</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C-2005</t>
+          <t>A-35-00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>P-000062</t>
+          <t>P-000025</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>package_dims</t>
+          <t>fitment</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r6</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -5742,7 +5848,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -5761,17 +5867,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A-35-00</t>
+          <t>B36L</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>P-000025</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5781,7 +5887,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -5789,7 +5895,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -5798,37 +5904,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MISSING_FITMENT</t>
+          <t>MISSING_PRICE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>缺少适配车型</t>
+          <t>缺少报价</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>B36L</t>
+          <t>A-33-00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P-000050</t>
+          <t>P-000024</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>fitment</t>
+          <t>price</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -5836,7 +5942,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5855,17 +5961,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A-33-00</t>
+          <t>B34X</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>P-000049</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5875,7 +5981,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -5883,7 +5989,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -5892,12 +5998,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MISSING_PRICE</t>
+          <t>SUSPECTED_NAME_ERROR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>缺少报价</t>
+          <t>包装尺寸 151 x 91 x 14 cm 与同车型的 3 条 Front Grille 一致（A:A-22-00, A:A-38-00, B:B06X），与同车型的 3 条 Bug Screen 都不同：疑似品名/类别或尺寸录错，请核对</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5907,22 +6013,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B34X</t>
+          <t>B39X</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>P-000049</t>
+          <t>P-000052</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -5930,7 +6036,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5939,27 +6045,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UNKNOWN_CATEGORY</t>
+          <t>SUSPECTED_NAME_ERROR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>无法从名称识别产品类别：Hood Latch</t>
+          <t>包装尺寸 124 x 77 x 10 cm 与同车型的 5 条 Front Grille 一致（A:A-11-00, A:A-24-00, A:A-33-00, B:B11X），同车型没有其他 Bug Screen 可对照：疑似品名/类别或尺寸录错，请核对</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A-44-00</t>
+          <t>B34X</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P-000056</t>
+          <t>P-000049</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5969,7 +6075,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R30</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -5977,7 +6083,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -5991,22 +6097,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>无法从名称识别产品类别：Grille</t>
+          <t>无法从名称识别产品类别：Hood Latch</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C-9001</t>
+          <t>A-44-00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>P-000065</t>
+          <t>P-000056</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6016,7 +6122,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p2!t1!r2</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -6024,21 +6130,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>警告</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CURRENCY_INFERRED</t>
+          <t>UNKNOWN_CATEGORY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>币种列为空，按价格符号推断为 USD</t>
+          <t>无法从名称识别产品类别：Grille</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6048,22 +6154,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-9001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P-000002</t>
+          <t>P-000064</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r3</t>
+          <t>供应商C目录.pdf!p2!t1!r2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -6071,7 +6177,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -6080,37 +6186,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MISSING_MOQ</t>
+          <t>CURRENCY_INFERRED</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>缺少 MOQ</t>
+          <t>币种列为空，按价格符号推断为 USD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B37X</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>P-000002</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>moq</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>供应商C目录.pdf!p1!t1!r3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -6118,7 +6224,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -6127,37 +6233,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MISSING_OE</t>
+          <t>MISSING_MOQ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>缺少 OE/交叉参考号</t>
+          <t>缺少 MOQ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>A-14-00</t>
+          <t>B37X</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>P-000013</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>oe_numbers</t>
+          <t>moq</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R14</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -6165,7 +6271,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -6189,12 +6295,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A-16-00</t>
+          <t>A-14-00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>P-000014</t>
+          <t>P-000013</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6204,7 +6310,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R15</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -6212,7 +6318,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -6236,12 +6342,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A-17-L</t>
+          <t>A-16-00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>P-000014</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6251,7 +6357,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R16</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -6259,7 +6365,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -6283,12 +6389,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>A-19-00</t>
+          <t>A-17-L</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>P-000016</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6298,7 +6404,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R17</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -6306,7 +6412,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -6330,12 +6436,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A-21-00</t>
+          <t>A-19-00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>P-000017</t>
+          <t>P-000016</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6345,7 +6451,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R18</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R17</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -6353,7 +6459,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -6377,12 +6483,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A-22-00</t>
+          <t>A-21-00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>P-000018</t>
+          <t>P-000017</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6392,7 +6498,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R19</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R18</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -6400,7 +6506,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -6424,12 +6530,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A-24-00</t>
+          <t>A-22-00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>P-000019</t>
+          <t>P-000018</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6439,7 +6545,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R20</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R19</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -6447,7 +6553,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -6471,12 +6577,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>A-25-L</t>
+          <t>A-24-00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>P-000020</t>
+          <t>P-000019</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -6486,7 +6592,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R21</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -6494,7 +6600,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -6518,12 +6624,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A-33-00</t>
+          <t>A-25-L</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>P-000020</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6533,7 +6639,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -6541,7 +6647,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -6565,12 +6671,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A-35-00</t>
+          <t>A-33-00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>P-000025</t>
+          <t>P-000024</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6580,7 +6686,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -6588,7 +6694,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6607,17 +6713,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>B15X</t>
+          <t>A-35-00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>P-000041</t>
+          <t>P-000025</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6627,7 +6733,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -6635,7 +6741,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6659,12 +6765,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>B18R</t>
+          <t>B15X</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6674,7 +6780,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -6682,7 +6788,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6706,12 +6812,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>B20X</t>
+          <t>B18R</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>P-000043</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6721,7 +6827,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -6729,7 +6835,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -6753,12 +6859,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>B23X</t>
+          <t>B20X</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>P-000044</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6768,7 +6874,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -6776,7 +6882,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -6800,12 +6906,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>B26R</t>
+          <t>B23X</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>P-000045</t>
+          <t>P-000044</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6815,7 +6921,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -6823,7 +6929,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -6847,12 +6953,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>B34X</t>
+          <t>B26R</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>P-000049</t>
+          <t>P-000045</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6862,7 +6968,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -6870,7 +6976,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -6894,12 +7000,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>B36L</t>
+          <t>B34X</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>P-000050</t>
+          <t>P-000049</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6909,7 +7015,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -6917,7 +7023,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -6941,12 +7047,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>B37X</t>
+          <t>B36L</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6956,7 +7062,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -6964,7 +7070,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -6983,17 +7089,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>A-43-R</t>
+          <t>B37X</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>P-000055</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -7003,7 +7109,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -7011,7 +7117,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -7030,17 +7136,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C-9001</t>
+          <t>A-43-R</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>P-000065</t>
+          <t>P-000055</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7050,7 +7156,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p2!t1!r2</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -7058,7 +7164,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -7067,40 +7173,87 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NOT_IN_LATEST</t>
+          <t>MISSING_OE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A-40-L 在最新文件 供应商A报价表_v2.xlsx 中未出现（未删除）</t>
+          <t>缺少 OE/交叉参考号</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A-40-L</t>
+          <t>C-9001</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>P-000027</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>P-000064</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>oe_numbers</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>供应商C目录.pdf!p2!t1!r2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>34</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>提示</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NOT_IN_LATEST</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>A-40-L 在最新文件 供应商A报价表_v2.xlsx 中未出现（未删除）</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>A-40-L</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>P-000027</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7111,7 +7264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7131,19 +7284,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>存在硬冲突的候选若选择 merge，必须在 note 说明理由。</t>
+          <t>“疑似组”相同的行相互关联（同一批相似记录），建议一起对照判断。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>异常清单 decision：resolve（已解决）/ ignore（忽略）。</t>
+          <t>存在硬冲突的候选若选择 merge，必须在 note 说明理由。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>异常清单 decision：resolve（已解决）/ ignore（忽略）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>任一行填写有误时整份文件不会写入，并逐行提示错误。</t>
         </is>

--- a/docs/samples/review_list.xlsx
+++ b/docs/samples/review_list.xlsx
@@ -12,8 +12,8 @@
     <sheet name="填写说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'疑似重复'!$A$1:$S$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'异常清单'!$A$1:$K$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'疑似重复'!$A$1:$S$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'异常清单'!$A$1:$K$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="39" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="70" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -641,7 +641,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>共用 OE 但关键属性冲突</t>
+          <t>共用 OE 但关键属性冲突；缺少关键信息</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A:A-31-L</t>
+          <t>A:A-12-L</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>B:B32R</t>
+          <t>B:B13R</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尺寸、车型年份</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>OE-SHARED-03 同时出现在 A:A-31-L（Side Grille）与 B:B32R（Side Grille），冲突：位置：A:A-31-L=left vs B:B32R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
+          <t>OE-VN-1010 同时出现在 A:A-12-L（Side Grille）与 B:B13R（Side Grille），冲突：位置：A:A-12-L=left vs B:B13R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 缺少尺寸、车型年份，判断依据不足。</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -722,7 +722,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
@@ -732,7 +732,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>共用 OE 但关键属性冲突</t>
+          <t>共用 OE 但关键属性冲突；同一供应商的两个编号；缺少关键信息</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -740,42 +740,42 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A:A-40-L</t>
+          <t>B:B12L</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>P-000057</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>B:B41R</t>
+          <t>B:B13R</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尺寸、车型年份</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>OE-CONFLICT-02 同时出现在 A:A-40-L（Side Grille）与 B:B41R（Side Grille），冲突：位置：A:A-40-L=left vs B:B41R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
+          <t>OE-VN-1010 同时出现在 B:B12L（Side Grille）与 B:B13R（Side Grille），冲突：位置：B:B12L=left vs B:B13R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 缺少尺寸、车型年份，判断依据不足。</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -803,25 +803,25 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>共用 OE 但关键属性冲突</t>
+          <t>共用 OE 但关键信息缺失；缺少关键信息</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.857</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A:A-03-L</t>
+          <t>A:A-12-L</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -831,47 +831,47 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P-000003</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C:C-1003-R</t>
+          <t>B:B12L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P-000059</t>
+          <t>P-000057</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>位置: left vs right</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>车型年份仅部分重叠</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>OE-VNL-1003 同时出现在 A:A-03-L（Side Grille）与 C:C-1003-R（Side Grille），冲突：位置：A:A-03-L=left vs C:C-1003-R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
+          <t>共用 OE-VN-1010，但车型年份仅部分重叠。请补充资料后重新导入，或在核实后确认合并。</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -884,17 +884,17 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -902,7 +902,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A:A-03-L</t>
+          <t>A:A-25-L</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -912,47 +912,47 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P-000003</t>
+          <t>P-000020</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>A:A-31-L</t>
+          <t>B:B12L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>P-000057</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1003 vs OE-SHARED-03（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1003 vs OE-SHARED-03），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -965,17 +965,17 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -983,57 +983,57 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A:A-03-L</t>
+          <t>B:B26R</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P-000003</t>
+          <t>P-000045</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>A:A-40-L</t>
+          <t>A:A-43-R</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Side Grille, Right side</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>P-000055</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1003 vs OE-CONFLICT-02（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1003 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1046,25 +1046,25 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号；缺少关键信息</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.619</v>
+        <v>0.476</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A:A-31-L</t>
+          <t>A:A-12-L</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A:A-40-L</t>
+          <t>A:A-25-L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1094,27 +1094,27 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>P-000020</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>OE 号: OE-SHARED-03 vs OE-CONFLICT-02（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号、车型年份仅部分重叠</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 车型年份仅部分重叠，判断依据不足。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1127,75 +1127,75 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同</t>
+          <t>无共同 OE，仅属性一致；缺少关键信息</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.619</v>
+        <v>0.476</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A:A-04-R</t>
+          <t>A:A-12-L</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Side Grille, Right side</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P-000004</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>B:B32R</t>
+          <t>B:B36L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1004 vs OE-SHARED-03（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号、适配车型</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-SHARED-03），可能是不同代次或替代件，请核对。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少适配车型，判断依据不足。</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1208,75 +1208,75 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B10" t="n">
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致；缺少关键信息</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.619</v>
+        <v>0.476</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>B:B04R</t>
+          <t>A:A-25-L</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P-000004</t>
+          <t>P-000020</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>B:B41R</t>
+          <t>B:B36L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1004 vs OE-CONFLICT-02（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号、适配车型</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少适配车型，判断依据不足。</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1289,75 +1289,75 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号；缺少关键信息</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.619</v>
+        <v>0.476</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>B:B32R</t>
+          <t>B:B12L</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>P-000057</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>B:B41R</t>
+          <t>B:B36L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Left Side Grille</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>OE 号: OE-SHARED-03 vs OE-CONFLICT-02（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号、适配车型</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 缺少适配车型，判断依据不足。</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1370,25 +1370,25 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号；缺少关键信息</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.619</v>
+        <v>0.476</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>B:B04R</t>
+          <t>B:B13R</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1398,47 +1398,47 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P-000004</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C:C-1003-R</t>
+          <t>B:B26R</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>P-000059</t>
+          <t>P-000045</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1004 vs OE-VNL-1003（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号、尺寸、车型年份</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 缺少尺寸、车型年份，判断依据不足。</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1451,25 +1451,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同</t>
+          <t>无共同 OE，仅属性一致；缺少关键信息</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.619</v>
+        <v>0.476</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>B:B32R</t>
+          <t>B:B13R</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1479,47 +1479,47 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C:C-1003-R</t>
+          <t>A:A-43-R</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Side Grille, Right side</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>P-000059</t>
+          <t>P-000055</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>OE 号: OE-SHARED-03 vs OE-VNL-1003（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号、尺寸、车型年份</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少尺寸、车型年份，判断依据不足。</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1532,65 +1532,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同</t>
+          <t>共用 OE 但关键属性冲突</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.619</v>
+        <v>0.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>B:B41R</t>
+          <t>A:A-31-L</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C:C-1003-R</t>
+          <t>B:B32R</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>P-000059</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>OE 号: OE-CONFLICT-02 vs OE-VNL-1003（软）</t>
+          <t>位置: left vs right</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-CONFLICT-02 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
+          <t>OE-SHARED-03 同时出现在 A:A-31-L（Side Grille）与 B:B32R（Side Grille），冲突：位置：A:A-31-L=left vs B:B32R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1613,25 +1613,25 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>共用 OE 但关键属性冲突</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.619</v>
+        <v>0.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A:A-03-L</t>
+          <t>A:A-40-L</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1641,47 +1641,47 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P-000003</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A:A-17-L</t>
+          <t>B:B41R</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>位置: left vs right</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE-CONFLICT-02 同时出现在 A:A-40-L（Side Grille）与 B:B41R（Side Grille），冲突：位置：A:A-40-L=left vs B:B41R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1694,25 +1694,25 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>共用 OE 但关键属性冲突</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.619</v>
+        <v>0.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>A:A-17-L</t>
+          <t>A:A-03-L</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1722,47 +1722,47 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>P-000003</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>A:A-31-L</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>P-000060</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>位置: left vs right</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE-VNL-1003 同时出现在 A:A-03-L（Side Grille）与 C:C-1003-R（Side Grille），冲突：位置：A:A-03-L=left vs C:C-1003-R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1775,17 +1775,17 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A:A-17-L</t>
+          <t>A:A-03-L</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>P-000003</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A:A-40-L</t>
+          <t>A:A-31-L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1823,27 +1823,27 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1003 vs OE-SHARED-03（软）</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>属性一致但 OE 号不同（OE-VNL-1003 vs OE-SHARED-03），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1856,17 +1856,17 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1874,57 +1874,57 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A:A-04-R</t>
+          <t>A:A-03-L</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Side Grille, Right side</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P-000004</t>
+          <t>P-000003</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>B:B18R</t>
+          <t>A:A-40-L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1003 vs OE-CONFLICT-02（软）</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>属性一致但 OE 号不同（OE-VNL-1003 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1937,17 +1937,17 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1955,57 +1955,57 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B:B18R</t>
+          <t>A:A-31-L</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>B:B32R</t>
+          <t>A:A-40-L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>OE 号: OE-SHARED-03 vs OE-CONFLICT-02（软）</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2018,17 +2018,17 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>属性一致但 OE 号不同</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2036,57 +2036,57 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B:B18R</t>
+          <t>A:A-04-R</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Side Grille, Right side</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>P-000004</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>B:B32R</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>Right Side Grille</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>P-000042</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>B:B41R</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Side Grille</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1004 vs OE-SHARED-03（软）</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-SHARED-03），可能是不同代次或替代件，请核对。</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2099,17 +2099,17 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>B:B18R</t>
+          <t>B:B04R</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2127,17 +2127,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>P-000004</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>C:C-1003-R</t>
+          <t>B:B41R</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2147,27 +2147,27 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>P-000059</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1004 vs OE-CONFLICT-02（软）</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2180,75 +2180,75 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>共用 OE 但关键属性冲突；缺少关键信息</t>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3</v>
+        <v>0.619</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A:A-12-L</t>
+          <t>B:B32R</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P-000012</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>B:B13R</t>
+          <t>B:B41R</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>位置: left vs right</t>
+          <t>OE 号: OE-SHARED-03 vs OE-CONFLICT-02（软）</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>尺寸、车型年份</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>OE-VN-1010 同时出现在 A:A-12-L（Side Grille）与 B:B13R（Side Grille），冲突：位置：A:A-12-L=left vs B:B13R=right。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 缺少尺寸、车型年份，判断依据不足。</t>
+          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-CONFLICT-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2261,17 +2261,17 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>属性一致但 OE 号不同</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2279,57 +2279,57 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A:A-12-L</t>
+          <t>B:B04R</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P-000012</t>
+          <t>P-000004</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A:A-25-L</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>P-000020</t>
+          <t>P-000060</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1004 vs OE-VNL-1003（软）</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>属性一致但 OE 号不同（OE-VNL-1004 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2342,17 +2342,17 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>属性一致但 OE 号不同</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>B:B26R</t>
+          <t>B:B32R</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2370,47 +2370,47 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P-000045</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A:A-43-R</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Side Grille, Right side</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>P-000055</t>
+          <t>P-000060</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>OE 号: OE-SHARED-03 vs OE-VNL-1003（软）</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>属性一致但 OE 号不同（OE-SHARED-03 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2423,75 +2423,75 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；缺少关键信息</t>
+          <t>属性一致但 OE 号不同</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.476</v>
+        <v>0.619</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A:A-12-L</t>
+          <t>B:B41R</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Side Grille, Left side</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P-000012</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>B:B36L</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Left Side Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>P-000050</t>
+          <t>P-000060</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
+          <t>OE 号: OE-CONFLICT-02 vs OE-VNL-1003（软）</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>OE 号、适配车型</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少适配车型，判断依据不足。</t>
+          <t>属性一致但 OE 号不同（OE-CONFLICT-02 vs OE-VNL-1003），可能是不同代次或替代件，请核对。</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2504,7 +2504,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
         <v>3</v>
@@ -2514,15 +2514,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；缺少关键信息</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.476</v>
+        <v>0.619</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A:A-25-L</t>
+          <t>A:A-03-L</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2532,32 +2532,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P-000020</t>
+          <t>P-000003</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>B:B36L</t>
+          <t>A:A-17-L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Left Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>P-000050</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>OE 号、适配车型</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少适配车型，判断依据不足。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2585,7 +2585,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="B27" t="n">
         <v>3</v>
@@ -2595,50 +2595,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号；缺少关键信息</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.476</v>
+        <v>0.619</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>B:B13R</t>
+          <t>A:A-17-L</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>B:B26R</t>
+          <t>A:A-31-L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>P-000045</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>OE 号、尺寸、车型年份</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 缺少尺寸、车型年份，判断依据不足。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2666,7 +2666,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="B28" t="n">
         <v>3</v>
@@ -2676,50 +2676,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；缺少关键信息</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.476</v>
+        <v>0.619</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>B:B13R</t>
+          <t>A:A-17-L</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Right Side Grille</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A:A-43-R</t>
+          <t>A:A-40-L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Side Grille, Right side</t>
+          <t>Side Grille, Left side</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>P-000055</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>OE 号、尺寸、车型年份</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 缺少尺寸、车型年份，判断依据不足。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2747,75 +2747,75 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="n">
         <v>4</v>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>共用 OE 但关键属性冲突；包装尺寸不同（仅提示）</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3</v>
+        <v>0.619</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A:A-27-00</t>
+          <t>A:A-04-R</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Side Grille, Right side</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P-000021</t>
+          <t>P-000004</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>B:B28X</t>
+          <t>B:B18R</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>P-000046</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>类别: Front Grille vs Bug Screen；尺寸: 122x75x7 vs 120x75x8（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>OE-SHARED-01 同时出现在 A:A-27-00（Front Grille）与 B:B28X（Bug Screen），冲突：类别：A:A-27-00=Front Grille vs B:B28X=Bug Screen。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 包装尺寸不同（122x75x7 vs 120x75x8），可能是换了包装，也可能是录入错误，仅作提示。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2828,75 +2828,75 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
-        <v>3</v>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.579</v>
+        <v>0.619</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A:A-01-00</t>
+          <t>B:B18R</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P-000001</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A:A-27-00</t>
+          <t>B:B32R</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>P-000021</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1001 vs OE-SHARED-01（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1001 vs OE-SHARED-01），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2909,75 +2909,75 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="n">
         <v>4</v>
       </c>
-      <c r="C31" t="n">
-        <v>3</v>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.579</v>
+        <v>0.619</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A:A-02-00</t>
+          <t>B:B18R</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P-000002</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>B:B28X</t>
+          <t>B:B41R</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>P-000046</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>OE 号: OE-VNL-1002 vs OE-SHARED-01（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-VNL-1002 vs OE-SHARED-01），可能是不同代次或替代件，请核对。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2990,60 +2990,60 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
         <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.579</v>
+        <v>0.619</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A:A-01-00</t>
+          <t>B:B18R</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Right Side Grille</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P-000001</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A:A-14-00</t>
+          <t>C:C-1003-R</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>P-000013</t>
+          <t>P-000060</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3071,75 +3071,75 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>共用 OE 但关键属性冲突；包装尺寸不同（仅提示）</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.579</v>
+        <v>0.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A:A-02-00</t>
+          <t>A:A-27-00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>P-000021</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>B:B28X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>Bug Screen</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>P-000002</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>A:A-16-00</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Bug Screen</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>P-000014</t>
+          <t>P-000046</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R15</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
+          <t>类别: Front Grille vs Bug Screen；尺寸: 122x75x7 vs 120x75x8（软）</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE-SHARED-01 同时出现在 A:A-27-00（Front Grille）与 B:B28X（Bug Screen），冲突：类别：A:A-27-00=Front Grille vs B:B28X=Bug Screen。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 包装尺寸不同（122x75x7 vs 120x75x8），可能是换了包装，也可能是录入错误，仅作提示。</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3152,17 +3152,17 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A:A-14-00</t>
+          <t>A:A-01-00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P-000013</t>
+          <t>P-000001</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1001 vs OE-SHARED-01（软）</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>属性一致但 OE 号不同（OE-VNL-1001 vs OE-SHARED-01），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3233,17 +3233,17 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>属性一致但 OE 号不同</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3251,57 +3251,57 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>A:A-01-00</t>
+          <t>A:A-02-00</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P-000001</t>
+          <t>P-000002</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>B:B15X</t>
+          <t>B:B28X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>P-000041</t>
+          <t>P-000046</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
+          <t>OE 号: OE-VNL-1002 vs OE-SHARED-01（软）</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>属性一致但 OE 号不同（OE-VNL-1002 vs OE-SHARED-01），可能是不同代次或替代件，请核对。</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3314,7 +3314,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="B36" t="n">
         <v>4</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3332,44 +3332,44 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>A:A-01-00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>P-000001</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>A:A-14-00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Front Grille</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>P-000013</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>B:B15X</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Front Grille</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>P-000041</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>—</t>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3395,7 +3395,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B37" t="n">
         <v>4</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3413,44 +3413,44 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>A:A-02-00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bug Screen</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>P-000002</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>A:A-16-00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Bug Screen</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>P-000014</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>供应商A报价表_v2.xlsx!报价明细!R15</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>B:B28X</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Bug Screen</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>P-000046</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>—</t>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3476,7 +3476,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="B38" t="n">
         <v>4</v>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3494,44 +3494,44 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>A:A-14-00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>P-000013</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>A:A-27-00</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Front Grille</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>P-000021</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>B:B15X</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Front Grille</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>P-000041</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>—</t>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3557,75 +3557,75 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>共用 OE 但关键属性冲突；包装尺寸不同（仅提示）</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.3</v>
+        <v>0.579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>A:A-29-00</t>
+          <t>A:A-01-00</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P-000022</t>
+          <t>P-000001</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>B:B30X</t>
+          <t>B:B15X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>类别: Air Filter Housing vs Air Filter Housing Cap；尺寸: 121x22x92 vs 32x32x8（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>OE-SHARED-02 同时出现在 A:A-29-00（Air Filter Housing）与 B:B30X（Air Filter Housing Cap），冲突：类别：A:A-29-00=Air Filter Housing vs B:B30X=Air Filter Housing Cap。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 包装尺寸不同（121x22x92 vs 32x32x8），可能是换了包装，也可能是录入错误，仅作提示。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3638,17 +3638,17 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3656,57 +3656,57 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>A:A-08-00</t>
+          <t>A:A-14-00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P-000008</t>
+          <t>P-000013</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A:A-29-00</t>
+          <t>B:B15X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>P-000022</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>OE 号: OE-FRC-2003 vs OE-SHARED-02（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-FRC-2003 vs OE-SHARED-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3719,17 +3719,17 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3737,57 +3737,57 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A:A-09-00</t>
+          <t>A:A-16-00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P-000009</t>
+          <t>P-000014</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>B:B30X</t>
+          <t>B:B28X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>P-000046</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>OE 号: OE-FRC-2004 vs OE-SHARED-02（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-FRC-2004 vs OE-SHARED-02），可能是不同代次或替代件，请核对。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3800,17 +3800,17 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
         <v>4</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3818,42 +3818,42 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>A:A-08-00</t>
+          <t>A:A-27-00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P-000008</t>
+          <t>P-000021</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>A:A-19-00</t>
+          <t>B:B15X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>P-000016</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R17</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3881,25 +3881,25 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="B43" t="n">
         <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>共用 OE 但关键属性冲突；包装尺寸不同（仅提示）</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.579</v>
+        <v>0.3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>A:A-19-00</t>
+          <t>A:A-29-00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3909,47 +3909,47 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P-000016</t>
+          <t>P-000022</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R17</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>A:A-29-00</t>
+          <t>B:B30X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>P-000022</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>类别: Air Filter Housing vs Air Filter Housing Cap；尺寸: 121x22x92 vs 32x32x8（软）</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>OE-SHARED-02 同时出现在 A:A-29-00（Air Filter Housing）与 B:B30X（Air Filter Housing Cap），冲突：类别：A:A-29-00=Air Filter Housing vs B:B30X=Air Filter Housing Cap。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。 包装尺寸不同（121x22x92 vs 32x32x8），可能是换了包装，也可能是录入错误，仅作提示。</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3962,17 +3962,17 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="B44" t="n">
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>属性一致但 OE 号不同；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -3980,57 +3980,57 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A:A-09-00</t>
+          <t>A:A-08-00</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P-000009</t>
+          <t>P-000008</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>B:B20X</t>
+          <t>A:A-29-00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>P-000043</t>
+          <t>P-000022</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
+          <t>OE 号: OE-FRC-2003 vs OE-SHARED-02（软）</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>属性一致但 OE 号不同（OE-FRC-2003 vs OE-SHARED-02），可能是不同代次或替代件，请核对。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4043,17 +4043,17 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" t="n">
         <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>属性一致但 OE 号不同</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>B:B37X</t>
+          <t>B:B30X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4091,27 +4091,27 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
+          <t>OE 号: OE-FRC-2004 vs OE-SHARED-02（软）</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>属性一致但 OE 号不同（OE-FRC-2004 vs OE-SHARED-02），可能是不同代次或替代件，请核对。</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4124,7 +4124,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="B46" t="n">
         <v>5</v>
@@ -4142,42 +4142,42 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>B:B20X</t>
+          <t>A:A-08-00</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P-000043</t>
+          <t>P-000008</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>B:B30X</t>
+          <t>A:A-19-00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>P-000016</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R17</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4205,7 +4205,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="B47" t="n">
         <v>5</v>
@@ -4223,42 +4223,42 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>B:B20X</t>
+          <t>A:A-19-00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P-000043</t>
+          <t>P-000016</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R17</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>B:B37X</t>
+          <t>A:A-29-00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>P-000022</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4286,7 +4286,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="B48" t="n">
         <v>5</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>B:B30X</t>
+          <t>A:A-09-00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4314,17 +4314,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>P-000009</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>B:B37X</t>
+          <t>B:B20X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4367,75 +4367,75 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>共用 OE 但关键属性冲突</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.3</v>
+        <v>0.579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>A:A-38-00</t>
+          <t>A:A-09-00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P-000026</t>
+          <t>P-000009</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>B:B39X</t>
+          <t>B:B37X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>P-000052</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>类别: Front Grille vs Bug Screen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>OE-CONFLICT-01 同时出现在 A:A-38-00（Front Grille）与 B:B39X（Bug Screen），冲突：类别：A:A-38-00=Front Grille vs B:B39X=Bug Screen。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4448,17 +4448,17 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -4466,57 +4466,57 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>A:A-38-00</t>
+          <t>B:B20X</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P-000026</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>B:B06X</t>
+          <t>B:B30X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>P-000006</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>OE 号: OE-CONFLICT-01 vs OE-FRC-2001（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-CONFLICT-01 vs OE-FRC-2001），可能是不同代次或替代件，请核对。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4529,75 +4529,75 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同；包装尺寸不同（仅提示）</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.421</v>
+        <v>0.579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>A:A-07-00</t>
+          <t>B:B20X</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P-000007</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R8</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>B:B39X</t>
+          <t>B:B37X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>P-000052</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>OE 号: OE-FRC-2002 vs OE-CONFLICT-01（软）；尺寸: 147x11x90 vs 151x91x14（软）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OE 号</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>属性一致但 OE 号不同（OE-FRC-2002 vs OE-CONFLICT-01），可能是不同代次或替代件，请核对。 包装尺寸不同（147x11x90 vs 151x91x14），可能是换了包装，也可能是录入错误，仅作提示。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4610,10 +4610,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" t="n">
         <v>4</v>
@@ -4628,42 +4628,42 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>A:A-22-00</t>
+          <t>B:B30X</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P-000018</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A:A-38-00</t>
+          <t>B:B37X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>P-000026</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4691,75 +4691,75 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="B53" t="n">
         <v>6</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>共用 OE 但关键属性冲突</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.579</v>
+        <v>0.3</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>A:A-07-00</t>
+          <t>A:A-38-00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>P-000026</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>B:B39X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>Bug Screen</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>P-000007</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R8</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>B:B23X</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Bug Screen</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>P-000044</t>
+          <t>P-000052</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
+          <t>类别: Front Grille vs Bug Screen</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>OE-CONFLICT-01 同时出现在 A:A-38-00（Front Grille）与 B:B39X（Bug Screen），冲突：类别：A:A-38-00=Front Grille vs B:B39X=Bug Screen。请向供应商核对 OE 号是否录错或是否为通用参考号；默认不合并。</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4772,17 +4772,17 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B54" t="n">
         <v>6</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致</t>
+          <t>属性一致但 OE 号不同</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A:A-22-00</t>
+          <t>A:A-38-00</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P-000018</t>
+          <t>P-000026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4830,17 +4830,17 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
+          <t>OE 号: OE-CONFLICT-01 vs OE-FRC-2001（软）</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>OE 号</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
+          <t>属性一致但 OE 号不同（OE-CONFLICT-01 vs OE-FRC-2001），可能是不同代次或替代件，请核对。</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4853,17 +4853,17 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132</v>
+        <v>51</v>
       </c>
       <c r="B55" t="n">
         <v>6</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号；包装尺寸不同（仅提示）</t>
+          <t>属性一致但 OE 号不同；包装尺寸不同（仅提示）</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>B:B23X</t>
+          <t>A:A-07-00</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P-000044</t>
+          <t>P-000007</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R8</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4911,17 +4911,17 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>尺寸: 147x11x90 vs 151x91x14（软）</t>
+          <t>OE 号: OE-FRC-2002 vs OE-CONFLICT-01（软）；尺寸: 147x11x90 vs 151x91x14（软）</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>OE 号</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 包装尺寸不同（147x11x90 vs 151x91x14），可能是换了包装，也可能是录入错误，仅作提示。</t>
+          <t>属性一致但 OE 号不同（OE-FRC-2002 vs OE-CONFLICT-01），可能是不同代次或替代件，请核对。 包装尺寸不同（147x11x90 vs 151x91x14），可能是换了包装，也可能是录入错误，仅作提示。</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4934,10 +4934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" t="n">
         <v>4</v>
@@ -4952,42 +4952,42 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>A:A-10-00</t>
+          <t>A:A-22-00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>P-000010</t>
+          <t>P-000018</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R11</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>A:A-21-00</t>
+          <t>A:A-38-00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>P-000017</t>
+          <t>P-000026</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R18</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5015,17 +5015,17 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C57" t="n">
         <v>4</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -5033,42 +5033,42 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>A:A-11-00</t>
+          <t>A:A-07-00</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P-000011</t>
+          <t>P-000007</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R8</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>A:A-24-00</t>
+          <t>B:B23X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>P-000019</t>
+          <t>P-000044</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5096,17 +5096,17 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="B58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C58" t="n">
         <v>4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>A:A-11-00</t>
+          <t>A:A-22-00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5124,17 +5124,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P-000011</t>
+          <t>P-000018</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A:A-33-00</t>
+          <t>B:B06X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>P-000006</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5177,65 +5177,65 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="B59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C59" t="n">
         <v>4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号；包装尺寸不同（仅提示）</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.579</v>
+        <v>0.421</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A:A-24-00</t>
+          <t>B:B23X</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>P-000019</t>
+          <t>P-000044</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>A:A-33-00</t>
+          <t>B:B39X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>P-000052</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尺寸: 147x11x90 vs 151x91x14（软）</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。 包装尺寸不同（147x11x90 vs 151x91x14），可能是换了包装，也可能是录入错误，仅作提示。</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5256,8 +5256,332 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>18</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>A:A-10-00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fan Shroud</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>P-000010</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R11</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>A:A-21-00</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Fan Shroud</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>P-000017</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R18</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>OE 号</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>20</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>A:A-11-00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>P-000011</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>A:A-24-00</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>P-000019</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>OE 号</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>21</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>A:A-11-00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>P-000011</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>A:A-33-00</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>P-000024</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>OE 号</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>30</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>无共同 OE，仅属性一致；同一供应商的两个编号</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>A:A-24-00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>P-000019</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>A:A-33-00</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>P-000024</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>OE 号</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>无共同 OE 号，仅类别/车型/尺寸相近；请查看图片或向供应商索要 OE 号后确认。 同一供应商的两个编号属性相近：可能是重复录入，也可能是不同品质档，请向供应商确认。</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S59"/>
+  <autoFilter ref="A1:S63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5268,7 +5592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5343,7 +5667,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -5390,7 +5714,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5433,7 +5757,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -5476,7 +5800,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -5505,7 +5829,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>P-000064</t>
+          <t>P-000065</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -5519,7 +5843,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -5533,7 +5857,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>关键属性变化：dims: [151.0, 91.0, 14.0] → [151.0, 91.0, 20.0]</t>
+          <t>关键属性变化：fitment: Volvo VN 2004-2017 → Volvo VN 2006-2017</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5543,12 +5867,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A-06-00</t>
+          <t>A-12-L</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>P-000006</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5558,7 +5882,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R7</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -5754,7 +6078,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -6083,7 +6407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -6130,7 +6454,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -6159,7 +6483,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P-000064</t>
+          <t>P-000065</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6177,7 +6501,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -7117,7 +7441,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -7164,7 +7488,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -7193,7 +7517,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>P-000064</t>
+          <t>P-000065</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7211,7 +7535,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -7252,8 +7576,55 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>31</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>提示</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PACKAGE_DIMS_CHANGED</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>包装尺寸变化：[151.0, 91.0, 14.0] → [151.0, 91.0, 20.0]（包装尺寸是辅助证据，按更新处理，不影响已归一关系）</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>A-06-00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>P-000006</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>package_dims</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>供应商A报价表_v2.xlsx!报价明细!R7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K42"/>
+  <autoFilter ref="A1:K43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/samples/review_list.xlsx
+++ b/docs/samples/review_list.xlsx
@@ -7637,6 +7637,9 @@
   </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
